--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4041" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4043" uniqueCount="367">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -529,10 +529,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -4785,7 +4788,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>166</v>
       </c>
@@ -4804,7 +4807,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4815,8 +4818,12 @@
       <c r="K33" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
+      <c r="L33" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4886,10 +4893,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4903,7 +4910,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4912,13 +4919,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4969,7 +4976,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4989,10 +4996,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5088,12 +5095,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5103,13 +5110,13 @@
         <v>62</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5122,7 +5129,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5134,7 +5141,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -5173,7 +5180,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5191,28 +5198,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5225,7 +5232,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5237,7 +5244,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5276,7 +5283,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5296,17 +5303,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5328,7 +5335,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5340,7 +5347,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5379,7 +5386,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5399,17 +5406,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5431,7 +5438,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5482,7 +5489,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5500,28 +5507,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5534,7 +5541,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5546,7 +5553,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5585,7 +5592,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5605,10 +5612,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5631,11 +5638,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5686,7 +5693,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5706,10 +5713,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5736,7 +5743,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5787,7 +5794,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5807,17 +5814,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5835,11 +5842,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5890,7 +5897,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5910,17 +5917,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5938,11 +5945,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5993,7 +6000,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6013,17 +6020,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -6041,11 +6048,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6096,7 +6103,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6116,10 +6123,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6133,7 +6140,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -6142,13 +6149,13 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6199,7 +6206,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6219,10 +6226,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6236,7 +6243,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6245,13 +6252,13 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6302,7 +6309,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6322,10 +6329,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6348,7 +6355,7 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6401,7 +6408,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6421,10 +6428,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6480,25 +6487,25 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6518,10 +6525,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6544,7 +6551,7 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6597,7 +6604,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6617,10 +6624,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6643,7 +6650,7 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6696,7 +6703,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6716,10 +6723,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6742,7 +6749,7 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -6795,7 +6802,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6815,10 +6822,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6832,7 +6839,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6841,7 +6848,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6882,7 +6889,7 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -6892,7 +6899,7 @@
         <v>124</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6912,13 +6919,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>74</v>
@@ -6940,7 +6947,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6993,7 +7000,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7013,10 +7020,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7114,10 +7121,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7215,10 +7222,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7316,10 +7323,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7417,10 +7424,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7520,10 +7527,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7623,10 +7630,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7726,10 +7733,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7829,10 +7836,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7930,10 +7937,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7963,7 +7970,7 @@
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
@@ -7989,7 +7996,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -8007,7 +8014,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8027,10 +8034,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8064,7 +8071,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>74</v>
@@ -8106,7 +8113,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8126,10 +8133,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8152,7 +8159,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8205,7 +8212,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8225,10 +8232,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8251,7 +8258,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8304,7 +8311,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8324,10 +8331,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8350,7 +8357,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8403,7 +8410,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8423,10 +8430,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8449,7 +8456,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8502,7 +8509,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8522,10 +8529,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8548,7 +8555,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8601,7 +8608,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8621,10 +8628,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8647,10 +8654,10 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -8702,7 +8709,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8722,10 +8729,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8748,7 +8755,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8801,7 +8808,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8821,10 +8828,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8847,7 +8854,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8900,7 +8907,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8920,10 +8927,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8946,7 +8953,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8999,7 +9006,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9019,13 +9026,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>74</v>
@@ -9047,7 +9054,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9100,7 +9107,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9120,10 +9127,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9221,10 +9228,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9322,10 +9329,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9423,10 +9430,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9524,10 +9531,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9627,10 +9634,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9730,10 +9737,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9833,10 +9840,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9936,10 +9943,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10037,10 +10044,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10070,7 +10077,7 @@
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
@@ -10096,7 +10103,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -10114,7 +10121,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10134,10 +10141,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10171,7 +10178,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>74</v>
@@ -10213,7 +10220,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10233,10 +10240,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10259,10 +10266,10 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
@@ -10314,7 +10321,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10334,10 +10341,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10360,7 +10367,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10413,7 +10420,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10433,10 +10440,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10459,7 +10466,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10512,7 +10519,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10532,10 +10539,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10558,7 +10565,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10611,7 +10618,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10631,10 +10638,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10657,7 +10664,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10710,7 +10717,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10730,10 +10737,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10756,7 +10763,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10809,7 +10816,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10829,10 +10836,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10855,7 +10862,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10908,7 +10915,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10928,10 +10935,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10954,7 +10961,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11007,7 +11014,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11027,10 +11034,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11053,7 +11060,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11106,7 +11113,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11126,13 +11133,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>74</v>
@@ -11154,7 +11161,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11207,7 +11214,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11227,10 +11234,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11328,10 +11335,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11429,10 +11436,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11530,10 +11537,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11631,10 +11638,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11734,10 +11741,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11837,10 +11844,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11940,10 +11947,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12043,10 +12050,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12144,10 +12151,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12177,7 +12184,7 @@
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
@@ -12203,7 +12210,7 @@
       </c>
       <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>74</v>
@@ -12221,7 +12228,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12241,10 +12248,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12278,7 +12285,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>74</v>
@@ -12320,7 +12327,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12340,10 +12347,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12366,7 +12373,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12419,7 +12426,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12439,10 +12446,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12465,7 +12472,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12518,7 +12525,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12538,10 +12545,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12564,10 +12571,10 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
@@ -12619,7 +12626,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12639,10 +12646,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12665,7 +12672,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12718,7 +12725,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12738,10 +12745,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12764,7 +12771,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12817,7 +12824,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12837,10 +12844,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12863,7 +12870,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -12916,7 +12923,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -12936,10 +12943,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -12962,7 +12969,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13015,7 +13022,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13035,10 +13042,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13061,7 +13068,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13114,7 +13121,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13134,10 +13141,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13160,7 +13167,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13213,7 +13220,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13233,10 +13240,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13259,7 +13266,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13312,7 +13319,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13332,10 +13339,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13433,10 +13440,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13534,10 +13541,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13635,10 +13642,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13736,10 +13743,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13839,10 +13846,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13942,10 +13949,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14045,10 +14052,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14148,10 +14155,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14249,10 +14256,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14279,7 +14286,7 @@
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14288,7 +14295,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>74</v>
@@ -14330,7 +14337,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14350,10 +14357,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14387,7 +14394,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>74</v>
@@ -14429,7 +14436,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14449,10 +14456,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14475,7 +14482,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14528,7 +14535,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
